--- a/assets/files/heads.xlsx
+++ b/assets/files/heads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\iism\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC524C02-1E22-4592-AF7D-45F35FC2D9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C06E292-3F0A-451E-BC5D-1F2A92BDC645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>Position</t>
   </si>
@@ -58,18 +58,12 @@
     <t>praveshm21@iitk.ac.in</t>
   </si>
   <si>
-    <t>Head, Finance</t>
-  </si>
-  <si>
     <t>Pratham Gupta</t>
   </si>
   <si>
     <t>prathamg21@iitk.c.in</t>
   </si>
   <si>
-    <t xml:space="preserve">Head , Media and Publicity </t>
-  </si>
-  <si>
     <t>Netraj Rane</t>
   </si>
   <si>
@@ -91,9 +85,6 @@
     <t>jayantn21@iitk.ac.in</t>
   </si>
   <si>
-    <t xml:space="preserve">Shivani </t>
-  </si>
-  <si>
     <t>shivani21@iitk.ac.in</t>
   </si>
   <si>
@@ -121,9 +112,6 @@
     <t>Head , Marketing</t>
   </si>
   <si>
-    <t xml:space="preserve">Sahil </t>
-  </si>
-  <si>
     <t>sahil21@iitk.ac.in</t>
   </si>
   <si>
@@ -163,9 +151,6 @@
     <t>mshekhar21@iitk.ac.in</t>
   </si>
   <si>
-    <t>Head , Web and App</t>
-  </si>
-  <si>
     <t>Ujjawal</t>
   </si>
   <si>
@@ -187,12 +172,6 @@
     <t>rudraksh22@iitk.ac.in</t>
   </si>
   <si>
-    <t xml:space="preserve">Head, Design </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shivam Rathore </t>
-  </si>
-  <si>
     <t>shivamr22@iitk.ac.in</t>
   </si>
   <si>
@@ -200,6 +179,24 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Shivam Rathore</t>
+  </si>
+  <si>
+    <t>Sahil</t>
+  </si>
+  <si>
+    <t>Shivani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head , Media &amp; Publicity </t>
+  </si>
+  <si>
+    <t>Head , Web &amp; App</t>
+  </si>
+  <si>
+    <t>Head , Finance</t>
   </si>
 </sst>
 </file>
@@ -502,7 +499,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
   </cols>
@@ -512,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -551,226 +548,226 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2">
-        <v>210678</v>
+        <v>220827</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2">
-        <v>210764</v>
+        <v>221152</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C6" s="2">
-        <v>210754</v>
+        <v>210666</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2">
-        <v>210664</v>
+        <v>210507</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2">
-        <v>211085</v>
+        <v>210497</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2">
-        <v>210467</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
+      <c r="A9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4">
+        <v>210597</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2">
-        <v>210985</v>
+        <v>210655</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2">
-        <v>210673</v>
+        <v>210593</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2">
-        <v>210655</v>
+        <v>211085</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2">
-        <v>210593</v>
+        <v>210664</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C14" s="2">
         <v>210893</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2">
         <v>210749</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C16" s="2">
-        <v>210507</v>
+        <v>210985</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2">
-        <v>210497</v>
+        <v>210673</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C18" s="2">
-        <v>210666</v>
+        <v>210467</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="4">
-        <v>210597</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>46</v>
+      <c r="A19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2">
+        <v>210754</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -792,61 +789,64 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C20" s="2">
-        <v>221152</v>
+        <v>210764</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2">
+        <v>210678</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3">
+        <v>221015</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="2">
-        <v>220827</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="2">
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="2">
         <v>220921</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="3">
-        <v>221015</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>57</v>
+      <c r="D23" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D24">
+    <sortCondition descending="1" ref="A1:A24"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/files/heads.xlsx
+++ b/assets/files/heads.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\iism\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C06E292-3F0A-451E-BC5D-1F2A92BDC645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3BBE7-EA7E-483B-9DF3-4DC1E72EEF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>Position</t>
   </si>
@@ -197,13 +197,19 @@
   </si>
   <si>
     <t>Head , Finance</t>
+  </si>
+  <si>
+    <t>Aakansh Chandra</t>
+  </si>
+  <si>
+    <t>aakanshc21@iitk.ac.in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -226,6 +232,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -257,10 +270,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -277,8 +291,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -495,7 +519,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -504,7 +528,7 @@
     <col min="4" max="4" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,7 +542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -532,7 +556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -546,7 +570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>57</v>
       </c>
@@ -560,7 +584,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>57</v>
       </c>
@@ -574,7 +598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -588,7 +612,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
@@ -602,7 +626,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -616,230 +640,243 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="6">
+        <v>210007</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C10" s="4">
         <v>210597</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2">
-        <v>210655</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>210655</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C12" s="2">
         <v>210593</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2">
-        <v>211085</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2">
+        <v>211085</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C14" s="2">
         <v>210664</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="2">
-        <v>210893</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2">
+        <v>210893</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C16" s="2">
         <v>210749</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2">
-        <v>210985</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2">
-        <v>210673</v>
+        <v>210985</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2">
+        <v>210673</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C19" s="2">
         <v>210467</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C20" s="2">
         <v>210754</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2">
-        <v>210764</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2">
+        <v>210764</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C22" s="2">
         <v>210678</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C23" s="3">
         <v>221015</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C24" s="2">
         <v>220921</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -847,6 +884,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D24">
     <sortCondition descending="1" ref="A1:A24"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{157A682D-DF24-4B87-B806-A7F198D9BD75}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/files/heads.xlsx
+++ b/assets/files/heads.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\iism\assets\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\iism\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3BBE7-EA7E-483B-9DF3-4DC1E72EEF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C26B1EE-1F7F-444C-A3FC-36EE21688592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="115">
   <si>
     <t>Position</t>
   </si>
@@ -115,12 +115,6 @@
     <t>sahil21@iitk.ac.in</t>
   </si>
   <si>
-    <t>Prasang Vashishtha</t>
-  </si>
-  <si>
-    <t>prasangv21@iitk.ac.in</t>
-  </si>
-  <si>
     <t xml:space="preserve">Head , Show Management </t>
   </si>
   <si>
@@ -203,13 +197,181 @@
   </si>
   <si>
     <t>aakanshc21@iitk.ac.in</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Linkedin</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/___avisharma___/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100057527562934</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sharma-avi/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mukul.saini63/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/mukul.saini.1291</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mukul-saini-40b478242/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pm020202pm/</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/pm020202pm/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_ujjwalchoudhary_/?hl=en</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ujjwal-choudhary-iitkanpur/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nikhilsharma.__/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nikhil-kumar-sharma-53b046252/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/keshav_chauhan_04/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/keshav.chauhan.12720?mibextid=ZbWKwL</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/keshav-chauhan-b02bbb231?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=android_app</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kartikv21/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100075444030031</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aakanshchandra/</t>
+  </si>
+  <si>
+    <t>www.linkedin.com/in/aakansh-chandra-43a0a6239</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mayank___shekhar/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mayank-shekhar-a71589232?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=android_app</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/naveen-meenia-639500283/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/manujaa08/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/manuja-pandey-095b26241/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sushant_faujdar_/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/sushant.faujdar</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sushantf21/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/netrajj?igsh=MTVkeDljcGZrZzkwdQ%3D%3D&amp;utm_source=qr</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100074911556032</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/netraj-pankaj-rane-517039224/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_sahiljangra07/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100075457655438</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sahil-jangra-286257241/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shixvani__/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/shivani-2107a9229?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=ios_app</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_nishantp_0605/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100015007967815</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nishant-patel-113b78231?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=android_app</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jayant_.nagar/?hl=en</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jayant-naagar/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/prath_2995?igsh=MXRuYXd2Nzhqd3M2Yw%3D%3D&amp;utm_source=qr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/pratham-gupta-a0b4321b8/?originalSubdomain=in</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pravesh_3553/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/1AzrB9ubRn/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/pravesh-meena-9b67aa229?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=android_app</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nitin-garhwal-03a71724b/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shiv.wrath_04/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/ngCeb8wvMHR4LQdG/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/shivam-rathore-559195259?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=android_app</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asliruddu/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100086966641157&amp;mibextid=LQQJ4d</t>
+  </si>
+  <si>
+    <t>https://github.com/pm020202pm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -240,6 +402,13 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -261,7 +430,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -269,12 +438,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -294,11 +478,26 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -519,30 +718,42 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
+    <col min="5" max="5" width="62.6640625" customWidth="1"/>
+    <col min="6" max="6" width="88.21875" customWidth="1"/>
+    <col min="7" max="7" width="57.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -552,11 +763,20 @@
       <c r="C2" s="2">
         <v>200230</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -569,107 +789,178 @@
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2">
         <v>220827</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2">
         <v>221152</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
         <v>210666</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2">
         <v>210507</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2">
         <v>210497</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="6">
         <v>210007</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4">
         <v>210597</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -682,8 +973,17 @@
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -696,10 +996,19 @@
       <c r="D12" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -710,10 +1019,19 @@
       <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -724,13 +1042,22 @@
       <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2">
         <v>210893</v>
@@ -738,155 +1065,271 @@
       <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2">
-        <v>210749</v>
+        <v>210985</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2">
-        <v>210985</v>
+        <v>210673</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" s="2">
-        <v>210673</v>
+        <v>210467</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C19" s="2">
-        <v>210467</v>
+        <v>210754</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" s="2">
-        <v>210754</v>
+        <v>210764</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2">
-        <v>210764</v>
+        <v>210678</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2">
-        <v>210678</v>
-      </c>
-      <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="E21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="3">
+        <v>221015</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2">
+        <v>220921</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="3">
-        <v>221015</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="2">
-        <v>220921</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>49</v>
+      <c r="E23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D24">
-    <sortCondition descending="1" ref="A1:A24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D23">
+    <sortCondition descending="1" ref="A1:A23"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="D9" r:id="rId1" xr:uid="{157A682D-DF24-4B87-B806-A7F198D9BD75}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{86A2727B-50AC-4728-8C91-A237964F84AC}"/>
+    <hyperlink ref="F2" r:id="rId3" xr:uid="{BD62D276-5D98-4E16-96F4-AF9CFD09B7FF}"/>
+    <hyperlink ref="G2" r:id="rId4" xr:uid="{365B0B81-07D4-46FC-856A-42F79AC8F2E0}"/>
+    <hyperlink ref="D2" r:id="rId5" xr:uid="{EB4C4BD3-5C8E-4948-8C21-3D739F57F3E8}"/>
+    <hyperlink ref="E3" r:id="rId6" xr:uid="{0DCA0CDD-2AE2-4AE5-8977-651597285D7A}"/>
+    <hyperlink ref="F3" r:id="rId7" xr:uid="{3953061F-0B4D-4E6E-970B-74C7CF216417}"/>
+    <hyperlink ref="G3" r:id="rId8" xr:uid="{708E19D2-C389-4217-BDC6-8077E9C7F610}"/>
+    <hyperlink ref="E4" r:id="rId9" xr:uid="{CBE18DBD-C6F4-45EC-9D8B-626A11051B86}"/>
+    <hyperlink ref="G4" r:id="rId10" xr:uid="{55828397-9869-45C9-822D-621BDD0CF381}"/>
+    <hyperlink ref="E5" r:id="rId11" xr:uid="{61C89ADF-D241-4A97-A38A-F71D789CCD26}"/>
+    <hyperlink ref="G5" r:id="rId12" xr:uid="{DD75C155-679E-496B-B8A8-9566BC3EA3A0}"/>
+    <hyperlink ref="E6" r:id="rId13" xr:uid="{4B8E8A7C-42C9-4FF3-97D7-A99FA56B550D}"/>
+    <hyperlink ref="G6" r:id="rId14" xr:uid="{AFC61B83-2E98-4284-9D0D-B3A60E0C10C5}"/>
+    <hyperlink ref="E7" r:id="rId15" display="https://www.instagram.com/keshav_chauhan_04/profilecard/?igsh=c2owMmlkNnFsNHU0" xr:uid="{B3F584E7-BE47-4D0C-8B43-D517F88FBC5C}"/>
+    <hyperlink ref="F7" r:id="rId16" xr:uid="{5C9944A7-674B-443E-9545-337AC1615FC2}"/>
+    <hyperlink ref="G7" r:id="rId17" xr:uid="{A5329E9C-5A6A-41C7-9425-AA38A597083A}"/>
+    <hyperlink ref="E8" r:id="rId18" xr:uid="{307AD88D-7867-4AA0-BA4D-A91A06A01135}"/>
+    <hyperlink ref="F8" r:id="rId19" xr:uid="{BE3DDE35-1374-47B6-9202-B36F41E8ADF7}"/>
+    <hyperlink ref="E9" r:id="rId20" xr:uid="{DB1C35D5-8F4C-45B9-BC0B-DFDA7A52EE4C}"/>
+    <hyperlink ref="G9" r:id="rId21" display="http://www.linkedin.com/in/aakansh-chandra-43a0a6239" xr:uid="{B562E6B2-1CC8-4F54-A43B-7B7F43702F71}"/>
+    <hyperlink ref="E10" r:id="rId22" xr:uid="{A95D0FBF-B526-44CA-8DB4-59DA21A0B8BD}"/>
+    <hyperlink ref="G10" r:id="rId23" xr:uid="{4D46E7A1-85A4-4A58-A66B-DA062F7C4644}"/>
+    <hyperlink ref="G11" r:id="rId24" xr:uid="{85FC84D5-44CF-41F7-87C0-E5813BF46D1D}"/>
+    <hyperlink ref="E12" r:id="rId25" xr:uid="{D259E487-0141-4314-973E-324BCEB97E2D}"/>
+    <hyperlink ref="G12" r:id="rId26" xr:uid="{6CA84CC4-4DC2-4702-8EEA-7C682A91FA4A}"/>
+    <hyperlink ref="E13" r:id="rId27" xr:uid="{9E892B45-1E1B-4007-B333-2329998C0082}"/>
+    <hyperlink ref="F13" r:id="rId28" xr:uid="{2A28044B-CE0B-4E6E-B8B6-906907798C10}"/>
+    <hyperlink ref="G13" r:id="rId29" xr:uid="{85EF480E-7097-46CD-BCF2-932F41438818}"/>
+    <hyperlink ref="E14" r:id="rId30" xr:uid="{A1FE2847-6A98-4696-B914-2DF656B375BF}"/>
+    <hyperlink ref="F14" r:id="rId31" xr:uid="{9DF6A810-D7A9-4E3C-B809-8EC3F6C5C4CE}"/>
+    <hyperlink ref="G14" r:id="rId32" xr:uid="{714FAA28-4F9D-4449-BB11-3B807B5F29A7}"/>
+    <hyperlink ref="E15" r:id="rId33" xr:uid="{54AC60C9-3AB9-4E4F-9D3E-287261D97E04}"/>
+    <hyperlink ref="F15" r:id="rId34" xr:uid="{AD183BB5-DB6D-4541-815F-356B36020B20}"/>
+    <hyperlink ref="G15" r:id="rId35" xr:uid="{9398A389-7D7C-40DC-9869-F4AC9646A263}"/>
+    <hyperlink ref="E16" r:id="rId36" xr:uid="{4B8088B2-92DF-4C6D-8240-DD8826E7F2DA}"/>
+    <hyperlink ref="F16" r:id="rId37" xr:uid="{2CBCA4C9-D780-4185-85B2-6CA3DBEC0071}"/>
+    <hyperlink ref="E17" r:id="rId38" display="https://www.instagram.com/_nishantp_0605/profilecard/?igsh=ZHJlNnA3bzMyM3U2" xr:uid="{0D725F93-84B9-4032-9C06-A3332C0666F1}"/>
+    <hyperlink ref="F17" r:id="rId39" xr:uid="{A0772829-A9FB-4AD5-9BBE-B87C73F9FF87}"/>
+    <hyperlink ref="G17" r:id="rId40" xr:uid="{D6460F9A-545D-489B-AA84-4528DA196CD3}"/>
+    <hyperlink ref="E18" r:id="rId41" xr:uid="{D8679275-68E4-41AB-9B5D-7287102C357C}"/>
+    <hyperlink ref="G18" r:id="rId42" xr:uid="{65D53500-3A51-46F8-998A-4A9B10F48FC3}"/>
+    <hyperlink ref="E19" r:id="rId43" xr:uid="{B1B72184-778B-4109-B640-76FA3B52AB51}"/>
+    <hyperlink ref="G19" r:id="rId44" xr:uid="{19F957F2-44E6-4E40-89E4-3EF350220B22}"/>
+    <hyperlink ref="E20" r:id="rId45" display="https://www.instagram.com/pravesh_3553/profilecard/?igsh=MTN6cG01anJmemU2eg==" xr:uid="{20AE1435-DEAB-408C-954D-DB517BDDD590}"/>
+    <hyperlink ref="F20" r:id="rId46" xr:uid="{B30BEE38-2077-4230-BB8C-488A9EFC2836}"/>
+    <hyperlink ref="G20" r:id="rId47" xr:uid="{71EDB69E-16A4-43D9-B70C-6BDFEC14F93C}"/>
+    <hyperlink ref="G21" r:id="rId48" xr:uid="{121E5105-8C78-4F4D-8F1F-F87A11AEEE69}"/>
+    <hyperlink ref="E22" r:id="rId49" display="https://www.instagram.com/shiv.wrath_04/profilecard/?igsh=ejZnbDR1NXRzbDQ0" xr:uid="{2D91D673-3080-409F-A9D7-F4D6EBEE36FF}"/>
+    <hyperlink ref="F22" r:id="rId50" xr:uid="{FDA164F5-15DB-4521-9C36-D0ED93749B37}"/>
+    <hyperlink ref="G22" r:id="rId51" xr:uid="{920444EF-E21C-4E35-A715-527B693D9332}"/>
+    <hyperlink ref="E23" r:id="rId52" display="https://www.instagram.com/asliruddu/profilecard/?igsh=c3VhdXFkb3JyeGd5" xr:uid="{C6A3099D-E57D-43DF-93AC-EA351ED5C252}"/>
+    <hyperlink ref="F23" r:id="rId53" xr:uid="{3495B7B8-F1CF-4667-BF4C-EC0244497AD8}"/>
+    <hyperlink ref="F4" r:id="rId54" xr:uid="{51CF9641-3168-4B54-B247-D8D14EB90E6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
 </worksheet>
 </file>